--- a/docs/control-plane/01_ACCOUNT_REGISTRY.xlsx
+++ b/docs/control-plane/01_ACCOUNT_REGISTRY.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="134">
   <si>
     <t>01_ACCOUNT_REGISTRY</t>
   </si>
@@ -46,6 +46,12 @@
     <t>CRITICAL: NEVER STORE PASSWORDS, API KEYS, SERVICE-ROLE KEYS, PRIVATE CERTIFICATES, SMTP PASSWORDS, OR R2 SECRETS IN THIS WORKBOOK. USE SECURE ENVIRONMENT REFERENCES ONLY.</t>
   </si>
   <si>
+    <t>Canonical Production Subdomain</t>
+  </si>
+  <si>
+    <t>https://erp.arivahly.in (Parent domain: arivahly.in)</t>
+  </si>
+  <si>
     <t>AI Operating Constraint 1</t>
   </si>
   <si>
@@ -70,10 +76,16 @@
     <t>UNKNOWN means unknown. Do not guess. If a field is uncertain, record NEEDS_VERIFICATION.</t>
   </si>
   <si>
+    <t>MCP Security Boundary</t>
+  </si>
+  <si>
+    <t>MCP is DISABLED and BLOCKED from public routing. MCP tools must remain internal/local only.</t>
+  </si>
+  <si>
     <t>Last Audit Date</t>
   </si>
   <si>
-    <t>2026-09-05T13:10:00+05:30 (Release v1.1.2-online-production-hardened)</t>
+    <t>2026-09-05T13:20:00+05:30 (Release v1.1.2-online-production-hardened)</t>
   </si>
   <si>
     <t>Account_ID</t>
@@ -181,7 +193,10 @@
     <t>ENV-ONLINE-PROD</t>
   </si>
   <si>
-    <t>maatarajewellers.shop</t>
+    <t>arivahly.in / erp.arivahly.in</t>
+  </si>
+  <si>
+    <t>erp.arivahly.in</t>
   </si>
   <si>
     <t>Shared hosting tier with cPanel/hPanel, native PHP 8.x</t>
@@ -202,10 +217,10 @@
     <t>DNS proxy, WAF, Bot Fight Mode, SSL/TLS</t>
   </si>
   <si>
-    <t>maatarajewellers.shop Zone</t>
-  </si>
-  <si>
-    <t>Proxies all web traffic to Hostinger origin</t>
+    <t>arivahly.in Zone</t>
+  </si>
+  <si>
+    <t>Proxies all erp.arivahly.in web traffic to Hostinger origin</t>
   </si>
   <si>
     <t>ACC-SUPABASE-PROD</t>
@@ -226,7 +241,7 @@
     <t>avs-gold-erp-production</t>
   </si>
   <si>
-    <t>Self-hosted / Cloud Supabase instance with active RLS</t>
+    <t>Cloud Supabase instance with active RLS</t>
   </si>
   <si>
     <t>ACC-CLOUDFLARE-R2</t>
@@ -295,7 +310,7 @@
     <t>Edge Proxy -&gt; Web Origin</t>
   </si>
   <si>
-    <t>Proxies HTTPS web &amp; API traffic to Hostinger web server</t>
+    <t>Proxies HTTPS web &amp; API traffic for erp.arivahly.in to Hostinger web server</t>
   </si>
   <si>
     <t>Full (Strict) SSL with WAF challenge and rate limits</t>
@@ -848,7 +863,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -933,6 +948,22 @@
       </c>
       <c r="B11" s="4" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -954,7 +985,7 @@
     <col min="6" max="6" width="23" customWidth="1"/>
     <col min="7" max="7" width="49" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="9" max="9" width="33" customWidth="1"/>
     <col min="10" max="10" width="27" customWidth="1"/>
     <col min="11" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="23" customWidth="1"/>
@@ -964,331 +995,331 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="M3" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="O3" s="6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="I4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="K4" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L4" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N5" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L6" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N6" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="N7" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -1315,176 +1346,176 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -1509,140 +1540,140 @@
   <sheetData>
     <row r="1" ht="26" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
